--- a/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
@@ -10405,10 +10405,10 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="Q79" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="R79" t="inlineStr">
         <is>
@@ -10421,13 +10421,13 @@
         </is>
       </c>
       <c r="T79" t="n">
-        <v>39840</v>
+        <v>278880</v>
       </c>
       <c r="U79" t="n">
-        <v>35000</v>
+        <v>185000</v>
       </c>
       <c r="V79" t="n">
-        <v>4840</v>
+        <v>93880</v>
       </c>
       <c r="W79" t="inlineStr"/>
       <c r="X79" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z79" t="inlineStr"/>
@@ -10452,13 +10452,13 @@
         </is>
       </c>
       <c r="AC79" t="n">
-        <v>0.44</v>
+        <v>6.4</v>
       </c>
       <c r="AD79" t="n">
-        <v>0.44</v>
+        <v>6.4</v>
       </c>
       <c r="AE79" t="n">
-        <v>0.44</v>
+        <v>6.4</v>
       </c>
     </row>
     <row r="80">

--- a/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE80"/>
+  <dimension ref="A1:AE83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10592,6 +10592,405 @@
       </c>
       <c r="AE80" t="n">
         <v>1.1</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>BW-2026-084</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>BW260033</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Bronislava Popovetsky</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>2 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>49×35×38cm(2CTN)</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0.134 CBM</t>
+        </is>
+      </c>
+      <c r="P81" t="n">
+        <v>27</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>21</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
+        <v>1007680</v>
+      </c>
+      <c r="U81" t="n">
+        <v>585000</v>
+      </c>
+      <c r="V81" t="n">
+        <v>422680</v>
+      </c>
+      <c r="W81" t="inlineStr"/>
+      <c r="X81" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr"/>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2549 Linden Street Bellmore, NY 11710</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>1 (646) 407-9686</t>
+        </is>
+      </c>
+      <c r="AC81" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AD81" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AE81" t="n">
+        <v>15.4</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>BW-2026-085</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>BW260034</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Maria Leonora A Dila</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>36×36×19cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0.025 CBM</t>
+        </is>
+      </c>
+      <c r="P82" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>5</v>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T82" t="n">
+        <v>255040</v>
+      </c>
+      <c r="U82" t="n">
+        <v>135000</v>
+      </c>
+      <c r="V82" t="n">
+        <v>120040</v>
+      </c>
+      <c r="W82" t="inlineStr"/>
+      <c r="X82" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr"/>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>31500 Grape St STE 3 Lake Elsinore, CA 92532</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>1 714-512-1776</t>
+        </is>
+      </c>
+      <c r="AC82" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>BW-2026-086</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>BW260035</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sharon Seng</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>(주)카스익스프레스</t>
+        </is>
+      </c>
+      <c r="J83" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr">
+        <is>
+          <t>보톡스</t>
+        </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>49×36×23cm(1CTN)</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0.042 CBM</t>
+        </is>
+      </c>
+      <c r="P83" t="n">
+        <v>9</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>8</v>
+      </c>
+      <c r="R83" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T83" t="n">
+        <v>362560</v>
+      </c>
+      <c r="U83" t="n">
+        <v>210000</v>
+      </c>
+      <c r="V83" t="n">
+        <v>152560</v>
+      </c>
+      <c r="W83" t="inlineStr"/>
+      <c r="X83" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr"/>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>921 Palo Cedro Dr Corona, California  92879</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>1 (657) 527-2068</t>
+        </is>
+      </c>
+      <c r="AC83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD83" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE83" t="n">
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
@@ -10130,7 +10130,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>335×21×13cm(1CTN)</t>
+          <t>33.5×21×13cm(1CTN)</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -10139,10 +10139,10 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="Q77" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="R77" t="inlineStr">
         <is>
@@ -10155,13 +10155,13 @@
         </is>
       </c>
       <c r="T77" t="n">
-        <v>756960</v>
+        <v>79680</v>
       </c>
       <c r="U77" t="n">
-        <v>410000</v>
+        <v>60000</v>
       </c>
       <c r="V77" t="n">
-        <v>346960</v>
+        <v>19680</v>
       </c>
       <c r="W77" t="inlineStr"/>
       <c r="X77" t="inlineStr">

--- a/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE83"/>
+  <dimension ref="A1:AE84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10991,6 +10991,135 @@
       </c>
       <c r="AE83" t="n">
         <v>7</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>수출 (Export)</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>BW-2026-087</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>BW260036</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>미국</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>대한민국 (KOREA)</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>넥서스파마 주식회사</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>DAMIAN RENATO JESUS MALO JUVER 8182189089</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>유에스퀵</t>
+        </is>
+      </c>
+      <c r="J84" t="inlineStr">
+        <is>
+          <t>항공(Air)</t>
+        </is>
+      </c>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>Door To Door</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>화장품</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1 박스 (CTN)</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>0.000 CBM</t>
+        </is>
+      </c>
+      <c r="P84" t="n">
+        <v>251</v>
+      </c>
+      <c r="Q84" t="n">
+        <v>249</v>
+      </c>
+      <c r="R84" t="inlineStr">
+        <is>
+          <t>📦 물류센터 입고 및 접수 완료</t>
+        </is>
+      </c>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>미수</t>
+        </is>
+      </c>
+      <c r="T84" t="n">
+        <v>5732840</v>
+      </c>
+      <c r="U84" t="n">
+        <v>4681200</v>
+      </c>
+      <c r="V84" t="n">
+        <v>1051640</v>
+      </c>
+      <c r="W84" t="inlineStr"/>
+      <c r="X84" t="inlineStr">
+        <is>
+          <t>이상복</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr"/>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>DAMIAN RENATO JESUS MALO JUVER # B 14411 EXPORT RD LAREDO TX 78045-7945</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr"/>
+      <c r="AC84" t="n">
+        <v>251</v>
+      </c>
+      <c r="AD84" t="n">
+        <v>251</v>
+      </c>
+      <c r="AE84" t="n">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
+++ b/범운해운항공_전체데이터_통합백업_2026-10-26.xlsx
@@ -11056,7 +11056,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>1 박스 (CTN)</t>
+          <t>19박스 (CTN)</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -11102,7 +11102,7 @@
       </c>
       <c r="Y84" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>이상복</t>
         </is>
       </c>
       <c r="Z84" t="inlineStr"/>
